--- a/versoes_fatorial/Versoes_Fatorial_numeros.xlsx
+++ b/versoes_fatorial/Versoes_Fatorial_numeros.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Versoes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cargas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Pares_por_eixo" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Estabilidade" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Indice_slides" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Versoes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cargas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pares_por_eixo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estabilidade" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indice_slides" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Versoes'!$A$1:$AY$109</definedName>
@@ -898,10 +898,10 @@
         <v>12.73409290193051</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.7962294478026549</v>
+        <v>0.7962956263600814</v>
       </c>
       <c r="AV2" t="n">
-        <v>38.62549830099587</v>
+        <v>36.76081200353045</v>
       </c>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
@@ -1069,10 +1069,10 @@
         <v>12.63893096458307</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.7960580954251195</v>
+        <v>0.7961242625042084</v>
       </c>
       <c r="AV3" t="n">
-        <v>38.64315029199335</v>
+        <v>36.76522506619594</v>
       </c>
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         <v>28.22268478594419</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.9244295831165088</v>
+        <v>0.9245140091770696</v>
       </c>
       <c r="AV4" t="n">
-        <v>22.50628852179285</v>
+        <v>21.68726095910562</v>
       </c>
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="inlineStr"/>
@@ -1411,10 +1411,10 @@
         <v>7.108881827778345</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.9464917157743044</v>
+        <v>0.946577430187674</v>
       </c>
       <c r="AV5" t="n">
-        <v>18.76995042732528</v>
+        <v>18.0435422182995</v>
       </c>
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="inlineStr"/>
@@ -1545,10 +1545,10 @@
         <v>60</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.8573123694290848</v>
+        <v>0.8573100073248491</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.8610885238855583</v>
+        <v>0.8610860554452898</v>
       </c>
       <c r="AJ6" t="n">
         <v>0.8358342537228167</v>
@@ -1586,10 +1586,10 @@
         <v>16.1678796259379</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.914627814584891</v>
+        <v>0.9146240470014328</v>
       </c>
       <c r="AV6" t="n">
-        <v>23.12116620820523</v>
+        <v>23.41571050308914</v>
       </c>
       <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         <v>60</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.8619274186705852</v>
+        <v>0.8619251329655953</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.8659758357001037</v>
+        <v>0.8659734541067798</v>
       </c>
       <c r="AJ7" t="n">
         <v>0.8467837148189055</v>
@@ -1757,10 +1757,10 @@
         <v>31.46463048194385</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.9367646934103387</v>
+        <v>0.936761902755585</v>
       </c>
       <c r="AV7" t="n">
-        <v>20.41305658934114</v>
+        <v>20.45013239187996</v>
       </c>
       <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="inlineStr"/>
@@ -1928,10 +1928,10 @@
         <v>5.093154206082823</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.9915619113056368</v>
+        <v>0.9916476234803988</v>
       </c>
       <c r="AV8" t="n">
-        <v>8.481781674291346</v>
+        <v>6.840247131509268</v>
       </c>
       <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="inlineStr"/>
@@ -2099,10 +2099,10 @@
         <v>5.022839027354133</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.9915987596473096</v>
+        <v>0.99168446574459</v>
       </c>
       <c r="AV9" t="n">
-        <v>8.49502066753946</v>
+        <v>6.831421006178287</v>
       </c>
       <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="inlineStr"/>
@@ -2270,10 +2270,10 @@
         <v>3.36314970865964</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.9885544281298668</v>
+        <v>0.9886418824150012</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.259940277430459</v>
+        <v>8.468667255075021</v>
       </c>
       <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="inlineStr"/>
@@ -2441,10 +2441,10 @@
         <v>3.397060894268773</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.9880927346543188</v>
+        <v>0.988180184092556</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.405569203159708</v>
+        <v>8.631950573698147</v>
       </c>
       <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="inlineStr"/>
@@ -2575,10 +2575,10 @@
         <v>60</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.8471110806654142</v>
+        <v>0.847108364426863</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.8472834032816051</v>
+        <v>0.8472806895259992</v>
       </c>
       <c r="AJ12" t="n">
         <v>0.8456388615702157</v>
@@ -2612,10 +2612,10 @@
         <v>3.425296150319862</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.992869973678698</v>
+        <v>0.9928696590215405</v>
       </c>
       <c r="AV12" t="n">
-        <v>8.692134567011371</v>
+        <v>7.449249779346867</v>
       </c>
       <c r="AW12" t="inlineStr"/>
       <c r="AX12" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
         <v>60</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.845419506683123</v>
+        <v>0.8454167603919134</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.8455918075583362</v>
+        <v>0.8455890637432772</v>
       </c>
       <c r="AJ13" t="n">
         <v>0.8424938707426901</v>
@@ -2780,13 +2780,13 @@
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
-        <v>3.460466819811521</v>
+        <v>3.460466819811497</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.9930316771930972</v>
+        <v>0.9930313696721218</v>
       </c>
       <c r="AV13" t="n">
-        <v>8.53032464953443</v>
+        <v>7.487496322447779</v>
       </c>
       <c r="AW13" t="inlineStr"/>
       <c r="AX13" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         <v>8.803949369138056</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.9685096220868183</v>
+        <v>0.9685936853190034</v>
       </c>
       <c r="AV14" t="n">
-        <v>18.76112443182654</v>
+        <v>14.79699911738747</v>
       </c>
       <c r="AW14" t="inlineStr"/>
       <c r="AX14" t="inlineStr"/>
@@ -3125,10 +3125,10 @@
         <v>8.636573341120835</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.9691819413996068</v>
+        <v>0.9692660495073258</v>
       </c>
       <c r="AV15" t="n">
-        <v>18.58607552110148</v>
+        <v>14.62783171521036</v>
       </c>
       <c r="AW15" t="inlineStr"/>
       <c r="AX15" t="inlineStr"/>
@@ -3296,10 +3296,10 @@
         <v>4.622545335338891</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.9839098858883312</v>
+        <v>0.9839969774125822</v>
       </c>
       <c r="AV16" t="n">
-        <v>10.85450346420323</v>
+        <v>10.14416004707267</v>
       </c>
       <c r="AW16" t="inlineStr"/>
       <c r="AX16" t="inlineStr"/>
@@ -3467,10 +3467,10 @@
         <v>4.628246073625621</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.9838440467637556</v>
+        <v>0.9839312103516732</v>
       </c>
       <c r="AV17" t="n">
-        <v>10.57648460599285</v>
+        <v>10.07208002353633</v>
       </c>
       <c r="AW17" t="inlineStr"/>
       <c r="AX17" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         <v>60</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.8452747182233505</v>
+        <v>0.8452721561647362</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.8512615145789825</v>
+        <v>0.8512588715139372</v>
       </c>
       <c r="AJ18" t="n">
         <v>0.8316115254958176</v>
@@ -3638,10 +3638,10 @@
         <v>4.495682832220201</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.9873281882006346</v>
+        <v>0.9873276289774136</v>
       </c>
       <c r="AV18" t="n">
-        <v>9.714479045615686</v>
+        <v>9.773462783171521</v>
       </c>
       <c r="AW18" t="inlineStr"/>
       <c r="AX18" t="inlineStr"/>
@@ -3772,10 +3772,10 @@
         <v>60</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.8461704668015644</v>
+        <v>0.8461679195754347</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.8520076176702672</v>
+        <v>0.8520049878633844</v>
       </c>
       <c r="AJ19" t="n">
         <v>0.8354099061136403</v>
@@ -3809,10 +3809,10 @@
         <v>4.462960313011583</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.9874236136114716</v>
+        <v>0.9874230585994958</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.623277092128683</v>
+        <v>9.711679905854664</v>
       </c>
       <c r="AW19" t="inlineStr"/>
       <c r="AX19" t="inlineStr"/>
@@ -3980,10 +3980,10 @@
         <v>4.689755243639048</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.991332270020998</v>
+        <v>0.9914178825789119</v>
       </c>
       <c r="AV20" t="n">
-        <v>12.5417396037128</v>
+        <v>8.681965283907031</v>
       </c>
       <c r="AW20" t="inlineStr"/>
       <c r="AX20" t="inlineStr"/>
@@ -4151,10 +4151,10 @@
         <v>37.51744940194848</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.9601570956028724</v>
+        <v>0.9602428569794847</v>
       </c>
       <c r="AV21" t="n">
-        <v>15.76028596225416</v>
+        <v>12.25801706384231</v>
       </c>
       <c r="AW21" t="inlineStr"/>
       <c r="AX21" t="inlineStr"/>
@@ -4322,10 +4322,10 @@
         <v>5.9601066286287</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.9991531880700965</v>
+        <v>0.9992413094194924</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.752239596357806</v>
+        <v>0.9944101206237128</v>
       </c>
       <c r="AW22" t="inlineStr"/>
       <c r="AX22" t="inlineStr"/>
@@ -4493,10 +4493,10 @@
         <v>8.037391236489025</v>
       </c>
       <c r="AU23" t="n">
-        <v>0.9907504248928974</v>
+        <v>0.9908382169610856</v>
       </c>
       <c r="AV23" t="n">
-        <v>6.209087833365206</v>
+        <v>6.19152691968226</v>
       </c>
       <c r="AW23" t="inlineStr"/>
       <c r="AX23" t="inlineStr"/>
@@ -4623,10 +4623,10 @@
         <v>60</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.8309270273203833</v>
+        <v>0.8309242284233568</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.8381304305147186</v>
+        <v>0.8381275541118846</v>
       </c>
       <c r="AJ24" t="n">
         <v>0.8186361864179833</v>
@@ -4794,10 +4794,10 @@
         <v>60</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.8427528355315506</v>
+        <v>0.8427502324033622</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.8482928557182123</v>
+        <v>0.8482901599004553</v>
       </c>
       <c r="AJ25" t="n">
         <v>0.8506017442967589</v>
@@ -4831,10 +4831,10 @@
         <v>9.979101867216871</v>
       </c>
       <c r="AU25" t="n">
-        <v>0.9866426380044624</v>
+        <v>0.9866420485270369</v>
       </c>
       <c r="AV25" t="n">
-        <v>7.875729983377708</v>
+        <v>7.596351868196528</v>
       </c>
       <c r="AW25" t="inlineStr"/>
       <c r="AX25" t="inlineStr"/>
@@ -4998,10 +4998,10 @@
         <v>4.083514401831015</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.9955144842916348</v>
+        <v>0.995600366332021</v>
       </c>
       <c r="AV26" t="n">
-        <v>5.532428178461629</v>
+        <v>4.69991173874669</v>
       </c>
       <c r="AW26" t="inlineStr"/>
       <c r="AX26" t="inlineStr"/>
@@ -5169,10 +5169,10 @@
         <v>4.012402678841355</v>
       </c>
       <c r="AU27" t="n">
-        <v>0.9955460452737456</v>
+        <v>0.995631923590828</v>
       </c>
       <c r="AV27" t="n">
-        <v>5.532428178461629</v>
+        <v>4.683730508973227</v>
       </c>
       <c r="AW27" t="inlineStr"/>
       <c r="AX27" t="inlineStr"/>
@@ -5340,10 +5340,10 @@
         <v>2.789069905654336</v>
       </c>
       <c r="AU28" t="n">
-        <v>0.9940085623201538</v>
+        <v>0.9940962316972128</v>
       </c>
       <c r="AV28" t="n">
-        <v>7.946337947367647</v>
+        <v>6.684318917328626</v>
       </c>
       <c r="AW28" t="inlineStr"/>
       <c r="AX28" t="inlineStr"/>
@@ -5511,10 +5511,10 @@
         <v>2.822249824839514</v>
       </c>
       <c r="AU29" t="n">
-        <v>0.9936943068036336</v>
+        <v>0.9937819855600331</v>
       </c>
       <c r="AV29" t="n">
-        <v>8.044894897103601</v>
+        <v>6.797587525742865</v>
       </c>
       <c r="AW29" t="inlineStr"/>
       <c r="AX29" t="inlineStr"/>
@@ -5645,10 +5645,10 @@
         <v>60</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.8346359187764677</v>
+        <v>0.8346329809030472</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.8348006646560923</v>
+        <v>0.8347977290837183</v>
       </c>
       <c r="AJ30" t="n">
         <v>0.8414284874310081</v>
@@ -5682,10 +5682,10 @@
         <v>2.649519303370921</v>
       </c>
       <c r="AU30" t="n">
-        <v>0.9960702777363268</v>
+        <v>0.99607010431267</v>
       </c>
       <c r="AV30" t="n">
-        <v>7.840426001382738</v>
+        <v>5.806119446896146</v>
       </c>
       <c r="AW30" t="inlineStr"/>
       <c r="AX30" t="inlineStr"/>
@@ -5816,10 +5816,10 @@
         <v>60</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.8353889173931367</v>
+        <v>0.8353859928975585</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.8355539818413119</v>
+        <v>0.835551059655294</v>
       </c>
       <c r="AJ31" t="n">
         <v>0.8423969724085913</v>
@@ -5853,10 +5853,10 @@
         <v>2.686280690009352</v>
       </c>
       <c r="AU31" t="n">
-        <v>0.996014722718613</v>
+        <v>0.9960145468432424</v>
       </c>
       <c r="AV31" t="n">
-        <v>7.911033965372678</v>
+        <v>5.89585172109444</v>
       </c>
       <c r="AW31" t="inlineStr"/>
       <c r="AX31" t="inlineStr"/>
@@ -6020,10 +6020,10 @@
         <v>6.427558326811514</v>
       </c>
       <c r="AU32" t="n">
-        <v>0.9953655466750804</v>
+        <v>0.995451125871372</v>
       </c>
       <c r="AV32" t="n">
-        <v>9.868933966843676</v>
+        <v>4.52633127390409</v>
       </c>
       <c r="AW32" t="inlineStr"/>
       <c r="AX32" t="inlineStr"/>
@@ -6191,10 +6191,10 @@
         <v>6.477346651250909</v>
       </c>
       <c r="AU33" t="n">
-        <v>0.9954556578974024</v>
+        <v>0.9955412973556784</v>
       </c>
       <c r="AV33" t="n">
-        <v>9.732131036613172</v>
+        <v>4.491026772580171</v>
       </c>
       <c r="AW33" t="inlineStr"/>
       <c r="AX33" t="inlineStr"/>
@@ -6358,10 +6358,10 @@
         <v>5.154707313221848</v>
       </c>
       <c r="AU34" t="n">
-        <v>0.9957348020372938</v>
+        <v>0.9958225162677832</v>
       </c>
       <c r="AV34" t="n">
-        <v>5.391212250481752</v>
+        <v>5.079435127978817</v>
       </c>
       <c r="AW34" t="inlineStr"/>
       <c r="AX34" t="inlineStr"/>
@@ -6529,10 +6529,10 @@
         <v>5.130154050840999</v>
       </c>
       <c r="AU35" t="n">
-        <v>0.9944051704576696</v>
+        <v>0.9944928906665008</v>
       </c>
       <c r="AV35" t="n">
-        <v>5.982553948897486</v>
+        <v>5.926743159752868</v>
       </c>
       <c r="AW35" t="inlineStr"/>
       <c r="AX35" t="inlineStr"/>
@@ -6663,10 +6663,10 @@
         <v>60</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.8288838812395081</v>
+        <v>0.8288810477689783</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.8357161015995827</v>
+        <v>0.8357131822944134</v>
       </c>
       <c r="AJ36" t="n">
         <v>0.8293367306753202</v>
@@ -6700,10 +6700,10 @@
         <v>4.817020831007804</v>
       </c>
       <c r="AU36" t="n">
-        <v>0.9971517278044312</v>
+        <v>0.9971516021065456</v>
       </c>
       <c r="AV36" t="n">
-        <v>4.592459657845574</v>
+        <v>4.6087084436599</v>
       </c>
       <c r="AW36" t="inlineStr"/>
       <c r="AX36" t="inlineStr"/>
@@ -6834,10 +6834,10 @@
         <v>60</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.8309849588344905</v>
+        <v>0.8309821601551978</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.8375433259323085</v>
+        <v>0.8375404390966965</v>
       </c>
       <c r="AJ37" t="n">
         <v>0.8348866196184686</v>
@@ -6871,10 +6871,10 @@
         <v>4.805058949532145</v>
       </c>
       <c r="AU37" t="n">
-        <v>0.9962657372595808</v>
+        <v>0.9962655724618024</v>
       </c>
       <c r="AV37" t="n">
-        <v>5.551551168708905</v>
+        <v>5.528096498970285</v>
       </c>
       <c r="AW37" t="inlineStr"/>
       <c r="AX37" t="inlineStr"/>
@@ -7046,10 +7046,10 @@
         <v>12.73473861921065</v>
       </c>
       <c r="AU38" t="n">
-        <v>0.7960319343093796</v>
+        <v>0.796098104150284</v>
       </c>
       <c r="AV38" t="n">
-        <v>38.58578132125153</v>
+        <v>36.70491320976758</v>
       </c>
       <c r="AW38" t="inlineStr"/>
       <c r="AX38" t="inlineStr"/>
@@ -7217,10 +7217,10 @@
         <v>12.63946015994292</v>
       </c>
       <c r="AU39" t="n">
-        <v>0.7958598717512246</v>
+        <v>0.79592603008245</v>
       </c>
       <c r="AV39" t="n">
-        <v>38.60196231299922</v>
+        <v>36.71079729332157</v>
       </c>
       <c r="AW39" t="inlineStr"/>
       <c r="AX39" t="inlineStr"/>
@@ -7388,10 +7388,10 @@
         <v>28.22217196116381</v>
       </c>
       <c r="AU40" t="n">
-        <v>0.9239273628642328</v>
+        <v>0.9240117667611734</v>
       </c>
       <c r="AV40" t="n">
-        <v>22.4077315720569</v>
+        <v>21.56075316269491</v>
       </c>
       <c r="AW40" t="inlineStr"/>
       <c r="AX40" t="inlineStr"/>
@@ -7559,10 +7559,10 @@
         <v>7.108325652898334</v>
       </c>
       <c r="AU41" t="n">
-        <v>0.9460105854838886</v>
+        <v>0.9460962786643649</v>
       </c>
       <c r="AV41" t="n">
-        <v>18.66698047983996</v>
+        <v>17.97734627831715</v>
       </c>
       <c r="AW41" t="inlineStr"/>
       <c r="AX41" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         <v>60</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.8576432775256304</v>
+        <v>0.8576409208993706</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.8614061474464249</v>
+        <v>0.8614036846502888</v>
       </c>
       <c r="AJ42" t="n">
         <v>0.8358342537228167</v>
@@ -7734,10 +7734,10 @@
         <v>16.1675738385036</v>
       </c>
       <c r="AU42" t="n">
-        <v>0.9141036815848192</v>
+        <v>0.9140998908707032</v>
       </c>
       <c r="AV42" t="n">
-        <v>23.02408025771907</v>
+        <v>23.31421006178288</v>
       </c>
       <c r="AW42" t="inlineStr"/>
       <c r="AX42" t="inlineStr"/>
@@ -7868,10 +7868,10 @@
         <v>60</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.8622853742471112</v>
+        <v>0.8622830944678512</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.8663227088291189</v>
+        <v>0.8663203333996889</v>
       </c>
       <c r="AJ43" t="n">
         <v>0.8467741935483871</v>
@@ -7905,10 +7905,10 @@
         <v>31.45982741458777</v>
       </c>
       <c r="AU43" t="n">
-        <v>0.9362313467547519</v>
+        <v>0.9362285325627298</v>
       </c>
       <c r="AV43" t="n">
-        <v>20.32626763360351</v>
+        <v>20.3898205354516</v>
       </c>
       <c r="AW43" t="inlineStr"/>
       <c r="AX43" t="inlineStr"/>
@@ -8076,10 +8076,10 @@
         <v>5.093017334949752</v>
       </c>
       <c r="AU44" t="n">
-        <v>0.9910199371332112</v>
+        <v>0.9911056253899616</v>
       </c>
       <c r="AV44" t="n">
-        <v>8.421470705049941</v>
+        <v>6.866725507502207</v>
       </c>
       <c r="AW44" t="inlineStr"/>
       <c r="AX44" t="inlineStr"/>
@@ -8247,10 +8247,10 @@
         <v>5.022699833196008</v>
       </c>
       <c r="AU45" t="n">
-        <v>0.991054556225804</v>
+        <v>0.9911402383066934</v>
       </c>
       <c r="AV45" t="n">
-        <v>8.433238699048264</v>
+        <v>6.862312444836717</v>
       </c>
       <c r="AW45" t="inlineStr"/>
       <c r="AX45" t="inlineStr"/>
@@ -8418,10 +8418,10 @@
         <v>3.363179617027877</v>
       </c>
       <c r="AU46" t="n">
-        <v>0.9881053560776176</v>
+        <v>0.9881927905446292</v>
       </c>
       <c r="AV46" t="n">
-        <v>9.323193245171444</v>
+        <v>8.528979111503384</v>
       </c>
       <c r="AW46" t="inlineStr"/>
       <c r="AX46" t="inlineStr"/>
@@ -8589,10 +8589,10 @@
         <v>3.397091790836948</v>
       </c>
       <c r="AU47" t="n">
-        <v>0.9876556921093086</v>
+        <v>0.9877431222603008</v>
       </c>
       <c r="AV47" t="n">
-        <v>9.470293170150484</v>
+        <v>8.686378346572521</v>
       </c>
       <c r="AW47" t="inlineStr"/>
       <c r="AX47" t="inlineStr"/>
@@ -8723,10 +8723,10 @@
         <v>60</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.8477614900763093</v>
+        <v>0.8477587853929913</v>
       </c>
       <c r="AI48" t="n">
-        <v>0.8478647359816204</v>
+        <v>0.8478620325562268</v>
       </c>
       <c r="AJ48" t="n">
         <v>0.8456379701838603</v>
@@ -8760,10 +8760,10 @@
         <v>3.425314874978256</v>
       </c>
       <c r="AU48" t="n">
-        <v>0.9923187752503188</v>
+        <v>0.9923184362680711</v>
       </c>
       <c r="AV48" t="n">
-        <v>8.771568526500051</v>
+        <v>7.519858781994704</v>
       </c>
       <c r="AW48" t="inlineStr"/>
       <c r="AX48" t="inlineStr"/>
@@ -8894,10 +8894,10 @@
         <v>60</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.8460598390896389</v>
+        <v>0.8460571041746335</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.8461631874806079</v>
+        <v>0.8461604538189017</v>
       </c>
       <c r="AJ49" t="n">
         <v>0.842492533663157</v>
@@ -8928,13 +8928,13 @@
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
-        <v>3.460487202006722</v>
+        <v>3.460487202006723</v>
       </c>
       <c r="AU49" t="n">
-        <v>0.9924463681786788</v>
+        <v>0.99244603482727</v>
       </c>
       <c r="AV49" t="n">
-        <v>8.6112296082729</v>
+        <v>7.55663430420712</v>
       </c>
       <c r="AW49" t="inlineStr"/>
       <c r="AX49" t="inlineStr"/>
@@ -9102,10 +9102,10 @@
         <v>8.804029264009209</v>
       </c>
       <c r="AU50" t="n">
-        <v>0.9678901683977114</v>
+        <v>0.9679742017772166</v>
       </c>
       <c r="AV50" t="n">
-        <v>18.64932848884247</v>
+        <v>14.6954986760812</v>
       </c>
       <c r="AW50" t="inlineStr"/>
       <c r="AX50" t="inlineStr"/>
@@ -9273,10 +9273,10 @@
         <v>8.636584085175841</v>
       </c>
       <c r="AU51" t="n">
-        <v>0.9685646532422446</v>
+        <v>0.968648736652678</v>
       </c>
       <c r="AV51" t="n">
-        <v>18.46839558111825</v>
+        <v>14.53368637834657</v>
       </c>
       <c r="AW51" t="inlineStr"/>
       <c r="AX51" t="inlineStr"/>
@@ -9444,10 +9444,10 @@
         <v>4.622281201955254</v>
       </c>
       <c r="AU52" t="n">
-        <v>0.9833303742225324</v>
+        <v>0.983417440172194</v>
       </c>
       <c r="AV52" t="n">
-        <v>10.79713449346141</v>
+        <v>10.11473962930274</v>
       </c>
       <c r="AW52" t="inlineStr"/>
       <c r="AX52" t="inlineStr"/>
@@ -9615,10 +9615,10 @@
         <v>4.627993038646472</v>
       </c>
       <c r="AU53" t="n">
-        <v>0.9832997131495944</v>
+        <v>0.9833868527153752</v>
       </c>
       <c r="AV53" t="n">
-        <v>10.52647063149998</v>
+        <v>10.03677552221242</v>
       </c>
       <c r="AW53" t="inlineStr"/>
       <c r="AX53" t="inlineStr"/>
@@ -9749,10 +9749,10 @@
         <v>60</v>
       </c>
       <c r="AH54" t="n">
-        <v>0.8457312012746202</v>
+        <v>0.8457286467747986</v>
       </c>
       <c r="AI54" t="n">
-        <v>0.8517291721654144</v>
+        <v>0.8517265374105885</v>
       </c>
       <c r="AJ54" t="n">
         <v>0.8316115254958176</v>
@@ -9786,10 +9786,10 @@
         <v>4.495397126948281</v>
       </c>
       <c r="AU54" t="n">
-        <v>0.986666722887415</v>
+        <v>0.986666134472886</v>
       </c>
       <c r="AV54" t="n">
-        <v>9.671820067371764</v>
+        <v>9.744042365401588</v>
       </c>
       <c r="AW54" t="inlineStr"/>
       <c r="AX54" t="inlineStr"/>
@@ -9875,10 +9875,10 @@
         <v>4</v>
       </c>
       <c r="U55" t="n">
-        <v>47.3810508487623</v>
+        <v>47.38105084876229</v>
       </c>
       <c r="V55" t="n">
-        <v>0.3907376209043069</v>
+        <v>0.3907376209043066</v>
       </c>
       <c r="W55" t="b">
         <v>1</v>
@@ -9893,7 +9893,7 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.045493624104076</v>
+        <v>0.0454936241040761</v>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         </is>
       </c>
       <c r="AC55" t="n">
-        <v>0.2285656060832946</v>
+        <v>0.228565606083295</v>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
@@ -9920,10 +9920,10 @@
         <v>60</v>
       </c>
       <c r="AH55" t="n">
-        <v>0.8466435945631152</v>
+        <v>0.846641055171394</v>
       </c>
       <c r="AI55" t="n">
-        <v>0.8524937644086421</v>
+        <v>0.8524911432405285</v>
       </c>
       <c r="AJ55" t="n">
         <v>0.8354103983869189</v>
@@ -9957,10 +9957,10 @@
         <v>4.462694588177879</v>
       </c>
       <c r="AU55" t="n">
-        <v>0.9867970640603146</v>
+        <v>0.9867964813979078</v>
       </c>
       <c r="AV55" t="n">
-        <v>9.599741104132036</v>
+        <v>9.689614592527214</v>
       </c>
       <c r="AW55" t="inlineStr"/>
       <c r="AX55" t="inlineStr"/>
@@ -10128,10 +10128,10 @@
         <v>4.690263463728773</v>
       </c>
       <c r="AU56" t="n">
-        <v>0.9905805380910002</v>
+        <v>0.990666117474044</v>
       </c>
       <c r="AV56" t="n">
-        <v>12.48584163222077</v>
+        <v>8.674610179464548</v>
       </c>
       <c r="AW56" t="inlineStr"/>
       <c r="AX56" t="inlineStr"/>
@@ -10299,10 +10299,10 @@
         <v>37.52023244946722</v>
       </c>
       <c r="AU57" t="n">
-        <v>0.9601286353781028</v>
+        <v>0.9602143976350532</v>
       </c>
       <c r="AV57" t="n">
-        <v>15.66025801326841</v>
+        <v>12.22271256251839</v>
       </c>
       <c r="AW57" t="inlineStr"/>
       <c r="AX57" t="inlineStr"/>
@@ -10470,10 +10470,10 @@
         <v>5.96013508119784</v>
       </c>
       <c r="AU58" t="n">
-        <v>0.9985497061573548</v>
+        <v>0.9986378008743244</v>
       </c>
       <c r="AV58" t="n">
-        <v>2.818434562598373</v>
+        <v>1.156222418358341</v>
       </c>
       <c r="AW58" t="inlineStr"/>
       <c r="AX58" t="inlineStr"/>
@@ -10641,10 +10641,10 @@
         <v>8.037874589916367</v>
       </c>
       <c r="AU59" t="n">
-        <v>0.9903939430130824</v>
+        <v>0.9904817193492702</v>
       </c>
       <c r="AV59" t="n">
-        <v>6.30617378385137</v>
+        <v>6.300382465431009</v>
       </c>
       <c r="AW59" t="inlineStr"/>
       <c r="AX59" t="inlineStr"/>
@@ -10771,10 +10771,10 @@
         <v>60</v>
       </c>
       <c r="AH60" t="n">
-        <v>0.8315412873063067</v>
+        <v>0.831538498577969</v>
       </c>
       <c r="AI60" t="n">
-        <v>0.8387735384484032</v>
+        <v>0.8387706734735201</v>
       </c>
       <c r="AJ60" t="n">
         <v>0.8186347095981474</v>
@@ -10812,10 +10812,10 @@
         <v>6.940487794862015</v>
       </c>
       <c r="AU60" t="n">
-        <v>0.9993782514527412</v>
+        <v>0.999378224014185</v>
       </c>
       <c r="AV60" t="n">
-        <v>0.1706359129756844</v>
+        <v>0.1838776110620771</v>
       </c>
       <c r="AW60" t="inlineStr"/>
       <c r="AX60" t="inlineStr"/>
@@ -10942,10 +10942,10 @@
         <v>60</v>
       </c>
       <c r="AH61" t="n">
-        <v>0.8433973810420174</v>
+        <v>0.8433947885838758</v>
       </c>
       <c r="AI61" t="n">
-        <v>0.8489641186573927</v>
+        <v>0.8489614347678975</v>
       </c>
       <c r="AJ61" t="n">
         <v>0.8506112655672773</v>
@@ -10979,10 +10979,10 @@
         <v>9.980018421450421</v>
       </c>
       <c r="AU61" t="n">
-        <v>0.9863169922409362</v>
+        <v>0.9863163883923474</v>
       </c>
       <c r="AV61" t="n">
-        <v>7.95810594136597</v>
+        <v>7.697852309502795</v>
       </c>
       <c r="AW61" t="inlineStr"/>
       <c r="AX61" t="inlineStr"/>
@@ -11146,10 +11146,10 @@
         <v>4.083650104769522</v>
       </c>
       <c r="AU62" t="n">
-        <v>0.9950780041655842</v>
+        <v>0.9951638669435452</v>
       </c>
       <c r="AV62" t="n">
-        <v>5.507421191215192</v>
+        <v>4.798470138275963</v>
       </c>
       <c r="AW62" t="inlineStr"/>
       <c r="AX62" t="inlineStr"/>
@@ -11317,10 +11317,10 @@
         <v>4.012520984646748</v>
       </c>
       <c r="AU63" t="n">
-        <v>0.9951072631768632</v>
+        <v>0.9951931221299318</v>
       </c>
       <c r="AV63" t="n">
-        <v>5.492711198717289</v>
+        <v>4.794057075610474</v>
       </c>
       <c r="AW63" t="inlineStr"/>
       <c r="AX63" t="inlineStr"/>
@@ -11488,10 +11488,10 @@
         <v>2.789285328583536</v>
       </c>
       <c r="AU64" t="n">
-        <v>0.9936136970742588</v>
+        <v>0.9937013490254106</v>
       </c>
       <c r="AV64" t="n">
-        <v>8.03459790235507</v>
+        <v>6.768167107972934</v>
       </c>
       <c r="AW64" t="inlineStr"/>
       <c r="AX64" t="inlineStr"/>
@@ -11659,10 +11659,10 @@
         <v>2.82247045866941</v>
       </c>
       <c r="AU65" t="n">
-        <v>0.993308097293523</v>
+        <v>0.993395759006004</v>
       </c>
       <c r="AV65" t="n">
-        <v>8.125799855842073</v>
+        <v>6.875551632833186</v>
       </c>
       <c r="AW65" t="inlineStr"/>
       <c r="AX65" t="inlineStr"/>
@@ -11793,10 +11793,10 @@
         <v>60</v>
       </c>
       <c r="AH66" t="n">
-        <v>0.8353836225053162</v>
+        <v>0.8353806979156685</v>
       </c>
       <c r="AI66" t="n">
-        <v>0.8354803516287836</v>
+        <v>0.8354774281343657</v>
       </c>
       <c r="AJ66" t="n">
         <v>0.8414342173220407</v>
@@ -11830,10 +11830,10 @@
         <v>2.649753488889586</v>
       </c>
       <c r="AU66" t="n">
-        <v>0.9955779513768024</v>
+        <v>0.9955777562261552</v>
       </c>
       <c r="AV66" t="n">
-        <v>7.922801959371001</v>
+        <v>5.88702559576346</v>
       </c>
       <c r="AW66" t="inlineStr"/>
       <c r="AX66" t="inlineStr"/>
@@ -11964,10 +11964,10 @@
         <v>60</v>
       </c>
       <c r="AH67" t="n">
-        <v>0.8361356175267244</v>
+        <v>0.8361327062970892</v>
       </c>
       <c r="AI67" t="n">
-        <v>0.8362326197948726</v>
+        <v>0.8362297096681697</v>
       </c>
       <c r="AJ67" t="n">
         <v>0.8423974181017689</v>
@@ -12001,10 +12001,10 @@
         <v>2.686519939643421</v>
       </c>
       <c r="AU67" t="n">
-        <v>0.9955303894746158</v>
+        <v>0.9955301922250012</v>
       </c>
       <c r="AV67" t="n">
-        <v>7.991938924111149</v>
+        <v>5.97822889085025</v>
       </c>
       <c r="AW67" t="inlineStr"/>
       <c r="AX67" t="inlineStr"/>
@@ -12168,10 +12168,10 @@
         <v>6.427683699864155</v>
       </c>
       <c r="AU68" t="n">
-        <v>0.9947671298446872</v>
+        <v>0.9948526826320808</v>
       </c>
       <c r="AV68" t="n">
-        <v>9.776261014106884</v>
+        <v>4.624889673433363</v>
       </c>
       <c r="AW68" t="inlineStr"/>
       <c r="AX68" t="inlineStr"/>
@@ -12339,10 +12339,10 @@
         <v>6.477461378811084</v>
       </c>
       <c r="AU69" t="n">
-        <v>0.9948623833481848</v>
+        <v>0.9949479966244978</v>
       </c>
       <c r="AV69" t="n">
-        <v>9.636516085376796</v>
+        <v>4.589585172109444</v>
       </c>
       <c r="AW69" t="inlineStr"/>
       <c r="AX69" t="inlineStr"/>
@@ -12506,10 +12506,10 @@
         <v>5.154916480766016</v>
       </c>
       <c r="AU70" t="n">
-        <v>0.9952451229318044</v>
+        <v>0.9953328155521304</v>
       </c>
       <c r="AV70" t="n">
-        <v>5.50006619496624</v>
+        <v>5.169167402177111</v>
       </c>
       <c r="AW70" t="inlineStr"/>
       <c r="AX70" t="inlineStr"/>
@@ -12677,10 +12677,10 @@
         <v>5.130403336768103</v>
       </c>
       <c r="AU71" t="n">
-        <v>0.9939577729919012</v>
+        <v>0.9940454734565112</v>
       </c>
       <c r="AV71" t="n">
-        <v>6.070813903884909</v>
+        <v>6.012062371285673</v>
       </c>
       <c r="AW71" t="inlineStr"/>
       <c r="AX71" t="inlineStr"/>
@@ -12811,10 +12811,10 @@
         <v>60</v>
       </c>
       <c r="AH72" t="n">
-        <v>0.8295129141615147</v>
+        <v>0.8295100911069894</v>
       </c>
       <c r="AI72" t="n">
-        <v>0.8363792562736734</v>
+        <v>0.8363763487526831</v>
       </c>
       <c r="AJ72" t="n">
         <v>0.8293347615822056</v>
@@ -12848,10 +12848,10 @@
         <v>4.817265602532207</v>
       </c>
       <c r="AU72" t="n">
-        <v>0.9965900836085932</v>
+        <v>0.9965899331246324</v>
       </c>
       <c r="AV72" t="n">
-        <v>4.69101660758153</v>
+        <v>4.711679905854664</v>
       </c>
       <c r="AW72" t="inlineStr"/>
       <c r="AX72" t="inlineStr"/>
@@ -12982,10 +12982,10 @@
         <v>60</v>
       </c>
       <c r="AH73" t="n">
-        <v>0.8316209700220797</v>
+        <v>0.8316181818743428</v>
       </c>
       <c r="AI73" t="n">
-        <v>0.8382135960227024</v>
+        <v>0.8382107210977094</v>
       </c>
       <c r="AJ73" t="n">
         <v>0.834884650525354</v>
@@ -13019,10 +13019,10 @@
         <v>4.805341222779488</v>
       </c>
       <c r="AU73" t="n">
-        <v>0.9957456532070688</v>
+        <v>0.9957454654573176</v>
       </c>
       <c r="AV73" t="n">
-        <v>5.645695120695488</v>
+        <v>5.620770814945572</v>
       </c>
       <c r="AW73" t="inlineStr"/>
       <c r="AX73" t="inlineStr"/>
@@ -13194,10 +13194,10 @@
         <v>12.73669369317089</v>
       </c>
       <c r="AU74" t="n">
-        <v>0.796032342045323</v>
+        <v>0.7960985119042212</v>
       </c>
       <c r="AV74" t="n">
-        <v>38.58578132125153</v>
+        <v>36.70491320976758</v>
       </c>
       <c r="AW74" t="inlineStr"/>
       <c r="AX74" t="inlineStr"/>
@@ -13365,10 +13365,10 @@
         <v>12.64128301630323</v>
       </c>
       <c r="AU75" t="n">
-        <v>0.7958602442086349</v>
+        <v>0.7959264025562972</v>
       </c>
       <c r="AV75" t="n">
-        <v>38.60196231299922</v>
+        <v>36.71079729332157</v>
       </c>
       <c r="AW75" t="inlineStr"/>
       <c r="AX75" t="inlineStr"/>
@@ -13536,10 +13536,10 @@
         <v>28.22462479301543</v>
       </c>
       <c r="AU76" t="n">
-        <v>0.9239474763091008</v>
+        <v>0.9240318810936732</v>
       </c>
       <c r="AV76" t="n">
-        <v>22.4077315720569</v>
+        <v>21.55928214180641</v>
       </c>
       <c r="AW76" t="inlineStr"/>
       <c r="AX76" t="inlineStr"/>
@@ -13707,10 +13707,10 @@
         <v>7.108466495786246</v>
       </c>
       <c r="AU77" t="n">
-        <v>0.9460286013976916</v>
+        <v>0.9461142953732332</v>
       </c>
       <c r="AV77" t="n">
-        <v>18.66550948059016</v>
+        <v>17.97587525742865</v>
       </c>
       <c r="AW77" t="inlineStr"/>
       <c r="AX77" t="inlineStr"/>
@@ -13841,10 +13841,10 @@
         <v>60</v>
       </c>
       <c r="AH78" t="n">
-        <v>0.8576377367383603</v>
+        <v>0.8576353800203762</v>
       </c>
       <c r="AI78" t="n">
-        <v>0.8614070234001707</v>
+        <v>0.8614045606196002</v>
       </c>
       <c r="AJ78" t="n">
         <v>0.8358342537228167</v>
@@ -13882,10 +13882,10 @@
         <v>16.16665719489644</v>
       </c>
       <c r="AU78" t="n">
-        <v>0.9141248886077192</v>
+        <v>0.9141210988294955</v>
       </c>
       <c r="AV78" t="n">
-        <v>23.02408025771907</v>
+        <v>23.31273904089438</v>
       </c>
       <c r="AW78" t="inlineStr"/>
       <c r="AX78" t="inlineStr"/>
@@ -14016,10 +14016,10 @@
         <v>60</v>
       </c>
       <c r="AH79" t="n">
-        <v>0.8622798943919776</v>
+        <v>0.8622776145220022</v>
       </c>
       <c r="AI79" t="n">
-        <v>0.8663229365467304</v>
+        <v>0.866320561121347</v>
       </c>
       <c r="AJ79" t="n">
         <v>0.8467932360894238</v>
@@ -14053,10 +14053,10 @@
         <v>31.47073883183933</v>
       </c>
       <c r="AU79" t="n">
-        <v>0.9362528276373112</v>
+        <v>0.936250014393268</v>
       </c>
       <c r="AV79" t="n">
-        <v>20.32185463585414</v>
+        <v>20.38834951456311</v>
       </c>
       <c r="AW79" t="inlineStr"/>
       <c r="AX79" t="inlineStr"/>
@@ -14224,10 +14224,10 @@
         <v>5.093357729597214</v>
       </c>
       <c r="AU80" t="n">
-        <v>0.991022402699881</v>
+        <v>0.9911080910654398</v>
       </c>
       <c r="AV80" t="n">
-        <v>8.422941704299731</v>
+        <v>6.866725507502207</v>
       </c>
       <c r="AW80" t="inlineStr"/>
       <c r="AX80" t="inlineStr"/>
@@ -14395,10 +14395,10 @@
         <v>5.023048370218838</v>
       </c>
       <c r="AU81" t="n">
-        <v>0.9910569418822994</v>
+        <v>0.9911426240684708</v>
       </c>
       <c r="AV81" t="n">
-        <v>8.428825701298893</v>
+        <v>6.86084142394822</v>
       </c>
       <c r="AW81" t="inlineStr"/>
       <c r="AX81" t="inlineStr"/>
@@ -14566,10 +14566,10 @@
         <v>3.363415957839197</v>
       </c>
       <c r="AU82" t="n">
-        <v>0.9881070357903536</v>
+        <v>0.9881944703314928</v>
       </c>
       <c r="AV82" t="n">
-        <v>9.323193245171444</v>
+        <v>8.528979111503384</v>
       </c>
       <c r="AW82" t="inlineStr"/>
       <c r="AX82" t="inlineStr"/>
@@ -14737,10 +14737,10 @@
         <v>3.397324197202503</v>
       </c>
       <c r="AU83" t="n">
-        <v>0.9876574434966509</v>
+        <v>0.9877448737249338</v>
       </c>
       <c r="AV83" t="n">
-        <v>9.467351171650902</v>
+        <v>8.686378346572521</v>
       </c>
       <c r="AW83" t="inlineStr"/>
       <c r="AX83" t="inlineStr"/>
@@ -14871,10 +14871,10 @@
         <v>60</v>
       </c>
       <c r="AH84" t="n">
-        <v>0.8477577060725664</v>
+        <v>0.8477550013220214</v>
       </c>
       <c r="AI84" t="n">
-        <v>0.8478625817730148</v>
+        <v>0.8478598783093413</v>
       </c>
       <c r="AJ84" t="n">
         <v>0.8456379701838603</v>
@@ -14908,10 +14908,10 @@
         <v>3.425552242651328</v>
       </c>
       <c r="AU84" t="n">
-        <v>0.9923203171993284</v>
+        <v>0.992319978285129</v>
       </c>
       <c r="AV84" t="n">
-        <v>8.768626528000471</v>
+        <v>7.519858781994704</v>
       </c>
       <c r="AW84" t="inlineStr"/>
       <c r="AX84" t="inlineStr"/>
@@ -15042,10 +15042,10 @@
         <v>60</v>
       </c>
       <c r="AH85" t="n">
-        <v>0.8460555602932307</v>
+        <v>0.8460528253022077</v>
       </c>
       <c r="AI85" t="n">
-        <v>0.8461607114311114</v>
+        <v>0.846157977725406</v>
       </c>
       <c r="AJ85" t="n">
         <v>0.8424934250495124</v>
@@ -15076,13 +15076,13 @@
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
-        <v>3.460719287832846</v>
+        <v>3.460719287832843</v>
       </c>
       <c r="AU85" t="n">
-        <v>0.9924476637052536</v>
+        <v>0.992447330411018</v>
       </c>
       <c r="AV85" t="n">
-        <v>8.609758609023109</v>
+        <v>7.55663430420712</v>
       </c>
       <c r="AW85" t="inlineStr"/>
       <c r="AX85" t="inlineStr"/>
@@ -15250,10 +15250,10 @@
         <v>8.806577257853945</v>
       </c>
       <c r="AU86" t="n">
-        <v>0.9679070769251475</v>
+        <v>0.967991113566246</v>
       </c>
       <c r="AV86" t="n">
-        <v>18.64638649034289</v>
+        <v>14.69255663430421</v>
       </c>
       <c r="AW86" t="inlineStr"/>
       <c r="AX86" t="inlineStr"/>
@@ -15421,10 +15421,10 @@
         <v>8.639226789049781</v>
       </c>
       <c r="AU87" t="n">
-        <v>0.9685820020150572</v>
+        <v>0.9686660861911142</v>
       </c>
       <c r="AV87" t="n">
-        <v>18.46545358261868</v>
+        <v>14.5233892321271</v>
       </c>
       <c r="AW87" t="inlineStr"/>
       <c r="AX87" t="inlineStr"/>
@@ -15592,10 +15592,10 @@
         <v>4.623445420508519</v>
       </c>
       <c r="AU88" t="n">
-        <v>0.983336143277227</v>
+        <v>0.9834232094814844</v>
       </c>
       <c r="AV88" t="n">
-        <v>10.78830849796267</v>
+        <v>10.11473962930274</v>
       </c>
       <c r="AW88" t="inlineStr"/>
       <c r="AX88" t="inlineStr"/>
@@ -15684,7 +15684,7 @@
         <v>49.606389640974</v>
       </c>
       <c r="V89" t="n">
-        <v>0.4451305859307628</v>
+        <v>0.4451305859307626</v>
       </c>
       <c r="W89" t="b">
         <v>1</v>
@@ -15707,7 +15707,7 @@
         </is>
       </c>
       <c r="AC89" t="n">
-        <v>0.2506707601961959</v>
+        <v>0.2506707601961961</v>
       </c>
       <c r="AD89" t="inlineStr">
         <is>
@@ -15763,10 +15763,10 @@
         <v>4.629115483784895</v>
       </c>
       <c r="AU89" t="n">
-        <v>0.983305027642379</v>
+        <v>0.9833921674426952</v>
       </c>
       <c r="AV89" t="n">
-        <v>10.5235286330004</v>
+        <v>10.03530450132392</v>
       </c>
       <c r="AW89" t="inlineStr"/>
       <c r="AX89" t="inlineStr"/>
@@ -15897,10 +15897,10 @@
         <v>60</v>
       </c>
       <c r="AH90" t="n">
-        <v>0.8457236521718287</v>
+        <v>0.8457210975470033</v>
       </c>
       <c r="AI90" t="n">
-        <v>0.8517258171259372</v>
+        <v>0.8517231823114925</v>
       </c>
       <c r="AJ90" t="n">
         <v>0.8316095564027032</v>
@@ -15934,10 +15934,10 @@
         <v>4.496516703600141</v>
       </c>
       <c r="AU90" t="n">
-        <v>0.986672342973454</v>
+        <v>0.986671754806946</v>
       </c>
       <c r="AV90" t="n">
-        <v>9.667407069622394</v>
+        <v>9.741100323624597</v>
       </c>
       <c r="AW90" t="inlineStr"/>
       <c r="AX90" t="inlineStr"/>
@@ -16068,10 +16068,10 @@
         <v>60</v>
       </c>
       <c r="AH91" t="n">
-        <v>0.8466362409084301</v>
+        <v>0.8466337013949414</v>
       </c>
       <c r="AI91" t="n">
-        <v>0.8524903729343469</v>
+        <v>0.8524877517059674</v>
       </c>
       <c r="AJ91" t="n">
         <v>0.8354118752067548</v>
@@ -16105,10 +16105,10 @@
         <v>4.463790116130291</v>
       </c>
       <c r="AU91" t="n">
-        <v>0.9868023600212098</v>
+        <v>0.9868017775925204</v>
       </c>
       <c r="AV91" t="n">
-        <v>9.598270104882246</v>
+        <v>9.689614592527214</v>
       </c>
       <c r="AW91" t="inlineStr"/>
       <c r="AX91" t="inlineStr"/>
@@ -16276,10 +16276,10 @@
         <v>4.689806548506733</v>
       </c>
       <c r="AU92" t="n">
-        <v>0.9905809070939584</v>
+        <v>0.9906664864932868</v>
       </c>
       <c r="AV92" t="n">
-        <v>12.48584163222077</v>
+        <v>8.674610179464548</v>
       </c>
       <c r="AW92" t="inlineStr"/>
       <c r="AX92" t="inlineStr"/>
@@ -16447,10 +16447,10 @@
         <v>37.51863743294283</v>
       </c>
       <c r="AU93" t="n">
-        <v>0.9601258883598478</v>
+        <v>0.9602116504955686</v>
       </c>
       <c r="AV93" t="n">
-        <v>15.6617290125182</v>
+        <v>12.22271256251839</v>
       </c>
       <c r="AW93" t="inlineStr"/>
       <c r="AX93" t="inlineStr"/>
@@ -16618,10 +16618,10 @@
         <v>5.959782505553147</v>
       </c>
       <c r="AU94" t="n">
-        <v>0.9985497479708902</v>
+        <v>0.9986378426897052</v>
       </c>
       <c r="AV94" t="n">
-        <v>2.819905561848163</v>
+        <v>1.156222418358341</v>
       </c>
       <c r="AW94" t="inlineStr"/>
       <c r="AX94" t="inlineStr"/>
@@ -16789,10 +16789,10 @@
         <v>8.037153482219567</v>
       </c>
       <c r="AU95" t="n">
-        <v>0.990396263297169</v>
+        <v>0.9904840397357538</v>
       </c>
       <c r="AV95" t="n">
-        <v>6.30617378385137</v>
+        <v>6.300382465431009</v>
       </c>
       <c r="AW95" t="inlineStr"/>
       <c r="AX95" t="inlineStr"/>
@@ -16919,10 +16919,10 @@
         <v>60</v>
       </c>
       <c r="AH96" t="n">
-        <v>0.831538266833294</v>
+        <v>0.8315354780549543</v>
       </c>
       <c r="AI96" t="n">
-        <v>0.8387729767449613</v>
+        <v>0.8387701117600967</v>
       </c>
       <c r="AJ96" t="n">
         <v>0.8186317559584758</v>
@@ -16960,10 +16960,10 @@
         <v>6.9397746701154</v>
       </c>
       <c r="AU96" t="n">
-        <v>0.99937825291355</v>
+        <v>0.9993782254750578</v>
       </c>
       <c r="AV96" t="n">
-        <v>0.1706359129756844</v>
+        <v>0.1838776110620771</v>
       </c>
       <c r="AW96" t="inlineStr"/>
       <c r="AX96" t="inlineStr"/>
@@ -17090,10 +17090,10 @@
         <v>60</v>
       </c>
       <c r="AH97" t="n">
-        <v>0.8433924959864606</v>
+        <v>0.84338990344745</v>
       </c>
       <c r="AI97" t="n">
-        <v>0.8489613298757096</v>
+        <v>0.848958645936658</v>
       </c>
       <c r="AJ97" t="n">
         <v>0.8506112655672773</v>
@@ -17127,10 +17127,10 @@
         <v>9.979381427224313</v>
       </c>
       <c r="AU97" t="n">
-        <v>0.9863208238867016</v>
+        <v>0.986320220207208</v>
       </c>
       <c r="AV97" t="n">
-        <v>7.95810594136597</v>
+        <v>7.697852309502795</v>
       </c>
       <c r="AW97" t="inlineStr"/>
       <c r="AX97" t="inlineStr"/>
@@ -17294,10 +17294,10 @@
         <v>4.083492959861402</v>
       </c>
       <c r="AU98" t="n">
-        <v>0.9950783076428912</v>
+        <v>0.9951641704342452</v>
       </c>
       <c r="AV98" t="n">
-        <v>5.505950191965402</v>
+        <v>4.796999117387466</v>
       </c>
       <c r="AW98" t="inlineStr"/>
       <c r="AX98" t="inlineStr"/>
@@ -17465,10 +17465,10 @@
         <v>4.012392052908869</v>
       </c>
       <c r="AU99" t="n">
-        <v>0.9951075357560762</v>
+        <v>0.995193394721174</v>
       </c>
       <c r="AV99" t="n">
-        <v>5.49418219796708</v>
+        <v>4.794057075610474</v>
       </c>
       <c r="AW99" t="inlineStr"/>
       <c r="AX99" t="inlineStr"/>
@@ -17636,10 +17636,10 @@
         <v>2.789197867903064</v>
       </c>
       <c r="AU100" t="n">
-        <v>0.9936134760195868</v>
+        <v>0.9937011279609832</v>
       </c>
       <c r="AV100" t="n">
-        <v>8.031655903855489</v>
+        <v>6.768167107972934</v>
       </c>
       <c r="AW100" t="inlineStr"/>
       <c r="AX100" t="inlineStr"/>
@@ -17807,10 +17807,10 @@
         <v>2.822372988206608</v>
       </c>
       <c r="AU101" t="n">
-        <v>0.993307850754896</v>
+        <v>0.9933955124564972</v>
       </c>
       <c r="AV101" t="n">
-        <v>8.125799855842073</v>
+        <v>6.875551632833186</v>
       </c>
       <c r="AW101" t="inlineStr"/>
       <c r="AX101" t="inlineStr"/>
@@ -17941,10 +17941,10 @@
         <v>60</v>
       </c>
       <c r="AH102" t="n">
-        <v>0.835382490893269</v>
+        <v>0.8353795662835171</v>
       </c>
       <c r="AI102" t="n">
-        <v>0.8354797413455846</v>
+        <v>0.8354768178403219</v>
       </c>
       <c r="AJ102" t="n">
         <v>0.8414346630152184</v>
@@ -17978,10 +17978,10 @@
         <v>2.649666028921022</v>
       </c>
       <c r="AU102" t="n">
-        <v>0.99557765958539</v>
+        <v>0.9955774644218658</v>
       </c>
       <c r="AV102" t="n">
-        <v>7.922801959371001</v>
+        <v>5.88702559576346</v>
       </c>
       <c r="AW102" t="inlineStr"/>
       <c r="AX102" t="inlineStr"/>
@@ -18112,10 +18112,10 @@
         <v>60</v>
       </c>
       <c r="AH103" t="n">
-        <v>0.8361346659108282</v>
+        <v>0.8361317546642866</v>
       </c>
       <c r="AI103" t="n">
-        <v>0.8362322083850543</v>
+        <v>0.8362292982510408</v>
       </c>
       <c r="AJ103" t="n">
         <v>0.8423969724085913</v>
@@ -18149,10 +18149,10 @@
         <v>2.686422070316037</v>
       </c>
       <c r="AU103" t="n">
-        <v>0.9955300871306244</v>
+        <v>0.9955298898676668</v>
       </c>
       <c r="AV103" t="n">
-        <v>7.991938924111149</v>
+        <v>5.97822889085025</v>
       </c>
       <c r="AW103" t="inlineStr"/>
       <c r="AX103" t="inlineStr"/>
@@ -18316,10 +18316,10 @@
         <v>6.427254291268052</v>
       </c>
       <c r="AU104" t="n">
-        <v>0.9947674644613343</v>
+        <v>0.9948530172634952</v>
       </c>
       <c r="AV104" t="n">
-        <v>9.776261014106884</v>
+        <v>4.623418652544866</v>
       </c>
       <c r="AW104" t="inlineStr"/>
       <c r="AX104" t="inlineStr"/>
@@ -18487,10 +18487,10 @@
         <v>6.47704141634608</v>
       </c>
       <c r="AU105" t="n">
-        <v>0.9948627567203144</v>
+        <v>0.9949483700131048</v>
       </c>
       <c r="AV105" t="n">
-        <v>9.639458083876375</v>
+        <v>4.589585172109444</v>
       </c>
       <c r="AW105" t="inlineStr"/>
       <c r="AX105" t="inlineStr"/>
@@ -18654,10 +18654,10 @@
         <v>5.154562652610972</v>
       </c>
       <c r="AU106" t="n">
-        <v>0.9952453834926264</v>
+        <v>0.995333076124451</v>
       </c>
       <c r="AV106" t="n">
-        <v>5.50006619496624</v>
+        <v>5.169167402177111</v>
       </c>
       <c r="AW106" t="inlineStr"/>
       <c r="AX106" t="inlineStr"/>
@@ -18825,10 +18825,10 @@
         <v>5.130038348664261</v>
       </c>
       <c r="AU107" t="n">
-        <v>0.9939581045002672</v>
+        <v>0.9940458049795072</v>
       </c>
       <c r="AV107" t="n">
-        <v>6.070813903884909</v>
+        <v>6.010591350397176</v>
       </c>
       <c r="AW107" t="inlineStr"/>
       <c r="AX107" t="inlineStr"/>
@@ -18959,10 +18959,10 @@
         <v>60</v>
       </c>
       <c r="AH108" t="n">
-        <v>0.8295109277535631</v>
+        <v>0.8295081046661453</v>
       </c>
       <c r="AI108" t="n">
-        <v>0.8363793989767099</v>
+        <v>0.8363764914582555</v>
       </c>
       <c r="AJ108" t="n">
         <v>0.8293367306753202</v>
@@ -18996,10 +18996,10 @@
         <v>4.816930284996209</v>
       </c>
       <c r="AU108" t="n">
-        <v>0.9965903272814076</v>
+        <v>0.9965901768082008</v>
       </c>
       <c r="AV108" t="n">
-        <v>4.686603609832159</v>
+        <v>4.711679905854664</v>
       </c>
       <c r="AW108" t="inlineStr"/>
       <c r="AX108" t="inlineStr"/>
@@ -19130,10 +19130,10 @@
         <v>60</v>
       </c>
       <c r="AH109" t="n">
-        <v>0.8316190902446314</v>
+        <v>0.8316163020657678</v>
       </c>
       <c r="AI109" t="n">
-        <v>0.8382136628198685</v>
+        <v>0.8382107878960625</v>
       </c>
       <c r="AJ109" t="n">
         <v>0.8348841582520754</v>
@@ -19167,10 +19167,10 @@
         <v>4.804998437496983</v>
       </c>
       <c r="AU109" t="n">
-        <v>0.9957459935506812</v>
+        <v>0.9957458058159496</v>
       </c>
       <c r="AV109" t="n">
-        <v>5.645695120695488</v>
+        <v>5.620770814945572</v>
       </c>
       <c r="AW109" t="inlineStr"/>
       <c r="AX109" t="inlineStr"/>
@@ -39941,25 +39941,25 @@
         <v>0</v>
       </c>
       <c r="E451" t="n">
-        <v>-0.001805030486349</v>
+        <v>-0.0018050304863491</v>
       </c>
       <c r="F451" t="n">
-        <v>0.720107803737381</v>
+        <v>0.7201078037373823</v>
       </c>
       <c r="G451" t="n">
-        <v>0.2795681795406208</v>
+        <v>0.2795681795406209</v>
       </c>
       <c r="H451" t="n">
-        <v>0.7194025104194854</v>
+        <v>0.7194025104194866</v>
       </c>
       <c r="I451" t="n">
-        <v>0.5175427326942501</v>
+        <v>0.5175427326942517</v>
       </c>
       <c r="J451" t="n">
         <v>0.7197431451578395</v>
       </c>
       <c r="K451" t="n">
-        <v>11.51639447817062</v>
+        <v>11.51639447817065</v>
       </c>
       <c r="L451" t="inlineStr">
         <is>
@@ -39987,25 +39987,25 @@
         <v>1</v>
       </c>
       <c r="E452" t="n">
-        <v>0.3440659066112907</v>
+        <v>0.3440659066112905</v>
       </c>
       <c r="F452" t="n">
         <v>0.460077465575101</v>
       </c>
       <c r="G452" t="n">
-        <v>0.5238354809417888</v>
+        <v>0.5238354809417886</v>
       </c>
       <c r="H452" t="n">
-        <v>0.5945169593586802</v>
+        <v>0.5945169593586801</v>
       </c>
       <c r="I452" t="n">
-        <v>0.453757785568555</v>
+        <v>0.4537577855685547</v>
       </c>
       <c r="J452" t="n">
         <v>0.8683543330304527</v>
       </c>
       <c r="K452" t="n">
-        <v>4.700926081774388</v>
+        <v>4.700926081774384</v>
       </c>
       <c r="L452" t="inlineStr">
         <is>
@@ -40033,25 +40033,25 @@
         <v>2</v>
       </c>
       <c r="E453" t="n">
-        <v>-0.038684540741538</v>
+        <v>-0.0386845407415378</v>
       </c>
       <c r="F453" t="n">
-        <v>0.4079013899997421</v>
+        <v>0.4079013899997418</v>
       </c>
       <c r="G453" t="n">
         <v>0.120697877950521</v>
       </c>
       <c r="H453" t="n">
-        <v>0.3927858845846179</v>
+        <v>0.3927858845846177</v>
       </c>
       <c r="I453" t="n">
-        <v>0.1555487663173498</v>
+        <v>0.1555487663173496</v>
       </c>
       <c r="J453" t="n">
         <v>0.6754339085201289</v>
       </c>
       <c r="K453" t="n">
-        <v>3.695148261722494</v>
+        <v>3.695148261722485</v>
       </c>
       <c r="L453" t="inlineStr">
         <is>
@@ -40079,25 +40079,25 @@
         <v>3</v>
       </c>
       <c r="E454" t="n">
-        <v>0.6871291834694883</v>
+        <v>0.6871291834694876</v>
       </c>
       <c r="F454" t="n">
-        <v>-0.1161763174256121</v>
+        <v>-0.1161763174256109</v>
       </c>
       <c r="G454" t="n">
-        <v>0.6417347255931809</v>
+        <v>0.6417347255931808</v>
       </c>
       <c r="H454" t="n">
-        <v>0.1523109049771746</v>
+        <v>0.1523109049771753</v>
       </c>
       <c r="I454" t="n">
-        <v>0.423259737956848</v>
+        <v>0.4232597379568475</v>
       </c>
       <c r="J454" t="n">
         <v>0.8543104620118136</v>
       </c>
       <c r="K454" t="n">
-        <v>10.58455315840626</v>
+        <v>10.58455315840624</v>
       </c>
       <c r="L454" t="inlineStr">
         <is>
@@ -40125,19 +40125,19 @@
         <v>4</v>
       </c>
       <c r="E455" t="n">
-        <v>0.8679309554089614</v>
+        <v>0.8679309554089616</v>
       </c>
       <c r="F455" t="n">
-        <v>-0.0189941141943597</v>
+        <v>-0.0189941141943601</v>
       </c>
       <c r="G455" t="n">
-        <v>0.8605092404174723</v>
+        <v>0.8605092404174726</v>
       </c>
       <c r="H455" t="n">
-        <v>0.3201391624313399</v>
+        <v>0.3201391624313394</v>
       </c>
       <c r="I455" t="n">
-        <v>0.7407818473644689</v>
+        <v>0.7407818473644691</v>
       </c>
       <c r="J455" t="n">
         <v>0.8246198855774779</v>
@@ -40171,19 +40171,19 @@
         <v>5</v>
       </c>
       <c r="E456" t="n">
-        <v>0.8933105016948552</v>
+        <v>0.8933105016948554</v>
       </c>
       <c r="F456" t="n">
-        <v>0.0161707822406891</v>
+        <v>0.0161707822406889</v>
       </c>
       <c r="G456" t="n">
-        <v>0.8996290346757434</v>
+        <v>0.8996290346757438</v>
       </c>
       <c r="H456" t="n">
-        <v>0.3652208024017697</v>
+        <v>0.3652208024017693</v>
       </c>
       <c r="I456" t="n">
-        <v>0.8095539703708553</v>
+        <v>0.8095539703708559</v>
       </c>
       <c r="J456" t="n">
         <v>0.7294385539664731</v>
@@ -40217,25 +40217,25 @@
         <v>6</v>
       </c>
       <c r="E457" t="n">
-        <v>0.8080676665016662</v>
+        <v>0.8080676665016665</v>
       </c>
       <c r="F457" t="n">
-        <v>0.1150481673706601</v>
+        <v>0.1150481673706602</v>
       </c>
       <c r="G457" t="n">
-        <v>0.8530213137094782</v>
+        <v>0.8530213137094788</v>
       </c>
       <c r="H457" t="n">
         <v>0.4307906049092161</v>
       </c>
       <c r="I457" t="n">
-        <v>0.7388606120607072</v>
+        <v>0.7388606120607081</v>
       </c>
       <c r="J457" t="n">
         <v>0.7925369861911712</v>
       </c>
       <c r="K457" t="n">
-        <v>14.63831873453551</v>
+        <v>14.63831873453552</v>
       </c>
       <c r="L457" t="inlineStr">
         <is>
@@ -40266,16 +40266,16 @@
         <v>0.07156911827552299</v>
       </c>
       <c r="F458" t="n">
-        <v>0.7174219829515927</v>
+        <v>0.7174219829515929</v>
       </c>
       <c r="G458" t="n">
         <v>0.3518928770784785</v>
       </c>
       <c r="H458" t="n">
-        <v>0.7453867299567896</v>
+        <v>0.7453867299567898</v>
       </c>
       <c r="I458" t="n">
-        <v>0.559941488811347</v>
+        <v>0.5599414888113473</v>
       </c>
       <c r="J458" t="n">
         <v>0.8217936524747096</v>
@@ -40309,7 +40309,7 @@
         <v>8</v>
       </c>
       <c r="E459" t="n">
-        <v>-0.1413136943499357</v>
+        <v>-0.1413136943499355</v>
       </c>
       <c r="F459" t="n">
         <v>0.5809958362719313</v>
@@ -40318,7 +40318,7 @@
         <v>0.0857032364702669</v>
       </c>
       <c r="H459" t="n">
-        <v>0.5257792595404391</v>
+        <v>0.5257792595404392</v>
       </c>
       <c r="I459" t="n">
         <v>0.2933645196277747</v>
@@ -40327,7 +40327,7 @@
         <v>0.8213448590549894</v>
       </c>
       <c r="K459" t="n">
-        <v>7.49665522602889</v>
+        <v>7.496655226028882</v>
       </c>
       <c r="L459" t="inlineStr">
         <is>
@@ -40355,25 +40355,25 @@
         <v>9</v>
       </c>
       <c r="E460" t="n">
-        <v>-0.0542732330878007</v>
+        <v>-0.0542732330878008</v>
       </c>
       <c r="F460" t="n">
-        <v>0.2285656060832946</v>
+        <v>0.228565606083295</v>
       </c>
       <c r="G460" t="n">
-        <v>0.0350359480537368</v>
+        <v>0.0350359480537367</v>
       </c>
       <c r="H460" t="n">
-        <v>0.2073590121077825</v>
+        <v>0.2073590121077828</v>
       </c>
       <c r="I460" t="n">
-        <v>0.045493624104076</v>
+        <v>0.0454936241040761</v>
       </c>
       <c r="J460" t="n">
         <v>0.6619439449515496</v>
       </c>
       <c r="K460" t="n">
-        <v>1.160227772502769</v>
+        <v>1.160227772502772</v>
       </c>
       <c r="L460" t="inlineStr">
         <is>
@@ -52870,16 +52870,16 @@
         <v>-0.0160917861131582</v>
       </c>
       <c r="F732" t="n">
-        <v>0.729545070612295</v>
+        <v>0.7295450706122952</v>
       </c>
       <c r="G732" t="n">
         <v>0.3086510386313923</v>
       </c>
       <c r="H732" t="n">
-        <v>0.7223821244310725</v>
+        <v>0.7223821244310726</v>
       </c>
       <c r="I732" t="n">
-        <v>0.5220435714798659</v>
+        <v>0.5220435714798661</v>
       </c>
       <c r="J732" t="n">
         <v>0.760254901842679</v>
@@ -52916,22 +52916,22 @@
         <v>0.3291122832365282</v>
       </c>
       <c r="F733" t="n">
-        <v>0.4770255233511563</v>
+        <v>0.4770255233511566</v>
       </c>
       <c r="G733" t="n">
-        <v>0.5414509339497572</v>
+        <v>0.5414509339497573</v>
       </c>
       <c r="H733" t="n">
-        <v>0.6235234668252434</v>
+        <v>0.6235234668252435</v>
       </c>
       <c r="I733" t="n">
-        <v>0.4756347612167943</v>
+        <v>0.4756347612167945</v>
       </c>
       <c r="J733" t="n">
         <v>0.883997719429817</v>
       </c>
       <c r="K733" t="n">
-        <v>4.52260069773453</v>
+        <v>4.522600697734533</v>
       </c>
       <c r="L733" t="inlineStr">
         <is>
@@ -52959,19 +52959,19 @@
         <v>2</v>
       </c>
       <c r="E734" t="n">
-        <v>-0.0561995442712742</v>
+        <v>-0.0561995442712743</v>
       </c>
       <c r="F734" t="n">
-        <v>0.434888668087337</v>
+        <v>0.4348886680873371</v>
       </c>
       <c r="G734" t="n">
-        <v>0.1373827033690911</v>
+        <v>0.1373827033690909</v>
       </c>
       <c r="H734" t="n">
         <v>0.409872532016823</v>
       </c>
       <c r="I734" t="n">
-        <v>0.1705280742142819</v>
+        <v>0.170528074214282</v>
       </c>
       <c r="J734" t="n">
         <v>0.7253908713205635</v>
@@ -53008,22 +53008,22 @@
         <v>0.6972894685648279</v>
       </c>
       <c r="F735" t="n">
-        <v>-0.1054362422132604</v>
+        <v>-0.10543624221326</v>
       </c>
       <c r="G735" t="n">
-        <v>0.6503565722901014</v>
+        <v>0.6503565722901017</v>
       </c>
       <c r="H735" t="n">
-        <v>0.2049486274923516</v>
+        <v>0.2049486274923518</v>
       </c>
       <c r="I735" t="n">
-        <v>0.4318777755402489</v>
+        <v>0.4318777755402492</v>
       </c>
       <c r="J735" t="n">
         <v>0.866172121519951</v>
       </c>
       <c r="K735" t="n">
-        <v>10.73717849108062</v>
+        <v>10.73717849108063</v>
       </c>
       <c r="L735" t="inlineStr">
         <is>
@@ -53051,25 +53051,25 @@
         <v>4</v>
       </c>
       <c r="E736" t="n">
-        <v>0.8760587407067243</v>
+        <v>0.8760587407067245</v>
       </c>
       <c r="F736" t="n">
         <v>-0.0269757875996821</v>
       </c>
       <c r="G736" t="n">
-        <v>0.8640509925665338</v>
+        <v>0.8640509925665344</v>
       </c>
       <c r="H736" t="n">
-        <v>0.3629847529608682</v>
+        <v>0.3629847529608681</v>
       </c>
       <c r="I736" t="n">
-        <v>0.7471676248564373</v>
+        <v>0.747167624856438</v>
       </c>
       <c r="J736" t="n">
         <v>0.8356971052568938</v>
       </c>
       <c r="K736" t="n">
-        <v>16.94846672303449</v>
+        <v>16.94846672303451</v>
       </c>
       <c r="L736" t="inlineStr">
         <is>
@@ -53100,16 +53100,16 @@
         <v>0.898156900010645</v>
       </c>
       <c r="F737" t="n">
-        <v>0.0106247872549869</v>
+        <v>0.0106247872549872</v>
       </c>
       <c r="G737" t="n">
-        <v>0.9028863177868468</v>
+        <v>0.9028863177868474</v>
       </c>
       <c r="H737" t="n">
         <v>0.4104218944144829</v>
       </c>
       <c r="I737" t="n">
-        <v>0.8152942215584031</v>
+        <v>0.8152942215584037</v>
       </c>
       <c r="J737" t="n">
         <v>0.743797515978543</v>
@@ -53143,25 +53143,25 @@
         <v>6</v>
       </c>
       <c r="E738" t="n">
-        <v>0.8103134997659974</v>
+        <v>0.810313499765997</v>
       </c>
       <c r="F738" t="n">
-        <v>0.1044547802635417</v>
+        <v>0.1044547802635428</v>
       </c>
       <c r="G738" t="n">
-        <v>0.8568095173079767</v>
+        <v>0.8568095173079771</v>
       </c>
       <c r="H738" t="n">
-        <v>0.4651501032019872</v>
+        <v>0.4651501032019879</v>
       </c>
       <c r="I738" t="n">
-        <v>0.7428714704221688</v>
+        <v>0.7428714704221695</v>
       </c>
       <c r="J738" t="n">
         <v>0.8057458351045296</v>
       </c>
       <c r="K738" t="n">
-        <v>14.50007035390414</v>
+        <v>14.50007035390413</v>
       </c>
       <c r="L738" t="inlineStr">
         <is>
@@ -53189,25 +53189,25 @@
         <v>7</v>
       </c>
       <c r="E739" t="n">
-        <v>0.06271484068386871</v>
+        <v>0.0627148406838683</v>
       </c>
       <c r="F739" t="n">
-        <v>0.736369368535602</v>
+        <v>0.7363693685356028</v>
       </c>
       <c r="G739" t="n">
-        <v>0.3904953691615871</v>
+        <v>0.3904953691615868</v>
       </c>
       <c r="H739" t="n">
-        <v>0.7642856623157671</v>
+        <v>0.7642856623157674</v>
       </c>
       <c r="I739" t="n">
-        <v>0.5872864054050331</v>
+        <v>0.587286405405034</v>
       </c>
       <c r="J739" t="n">
         <v>0.837770501197428</v>
       </c>
       <c r="K739" t="n">
-        <v>10.77696421863179</v>
+        <v>10.77696421863181</v>
       </c>
       <c r="L739" t="inlineStr">
         <is>
@@ -53235,25 +53235,25 @@
         <v>8</v>
       </c>
       <c r="E740" t="n">
-        <v>-0.0817708220663786</v>
+        <v>-0.0817708220663783</v>
       </c>
       <c r="F740" t="n">
-        <v>0.67719662926598</v>
+        <v>0.6771966292659798</v>
       </c>
       <c r="G740" t="n">
-        <v>0.2196701103091246</v>
+        <v>0.2196701103091247</v>
       </c>
       <c r="H740" t="n">
-        <v>0.6407979353275329</v>
+        <v>0.6407979353275327</v>
       </c>
       <c r="I740" t="n">
-        <v>0.4159835963410155</v>
+        <v>0.4159835963410153</v>
       </c>
       <c r="J740" t="n">
         <v>0.863728651861165</v>
       </c>
       <c r="K740" t="n">
-        <v>9.114536480958652</v>
+        <v>9.114536480958639</v>
       </c>
       <c r="L740" t="inlineStr">
         <is>
@@ -53281,16 +53281,16 @@
         <v>9</v>
       </c>
       <c r="E741" t="n">
-        <v>-0.0720084763164547</v>
+        <v>-0.07200847631645479</v>
       </c>
       <c r="F741" t="n">
-        <v>0.2506707601961959</v>
+        <v>0.2506707601961961</v>
       </c>
       <c r="G741" t="n">
-        <v>0.0395727460453877</v>
+        <v>0.0395727460453876</v>
       </c>
       <c r="H741" t="n">
-        <v>0.218617584941471</v>
+        <v>0.2186175849414711</v>
       </c>
       <c r="I741" t="n">
         <v>0.0519514630631486</v>
@@ -53299,7 +53299,7 @@
         <v>0.7132602781732882</v>
       </c>
       <c r="K741" t="n">
-        <v>1.248856010111506</v>
+        <v>1.248856010111507</v>
       </c>
       <c r="L741" t="inlineStr">
         <is>
@@ -60936,7 +60936,7 @@
         <v>6.175584210232898e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0006244753196464</v>
+        <v>0.0006244810336218</v>
       </c>
       <c r="S2" t="n">
         <v>0.0003074202937501</v>
@@ -60963,7 +60963,7 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.9994126459430116</v>
+        <v>0.999412620022328</v>
       </c>
       <c r="AB2" t="n">
         <v>0.9992992998678936</v>
@@ -60972,13 +60972,13 @@
         <v>0.99960626421688</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.1868169047233785</v>
+        <v>0.1934378078633405</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.0912019534870037</v>
+        <v>0.1059119459849075</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2118238919698151</v>
+        <v>0.219178888218767</v>
       </c>
     </row>
     <row r="3">
@@ -61040,7 +61040,7 @@
         <v>1.348326726535731e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0006232448854852</v>
+        <v>0.0006232505944699</v>
       </c>
       <c r="S3" t="n">
         <v>0.000307304916827</v>
@@ -61067,7 +61067,7 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.99941263857226</v>
+        <v>0.999412612651251</v>
       </c>
       <c r="AB3" t="n">
         <v>0.9992993291986884</v>
@@ -61076,13 +61076,13 @@
         <v>0.9996062611363672</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.1882879039731689</v>
+        <v>0.1934378078633405</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.0912019534870037</v>
+        <v>0.1059119459849075</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2118238919698151</v>
+        <v>0.219178888218767</v>
       </c>
     </row>
     <row r="4">
@@ -61147,7 +61147,7 @@
         <v>-4.713754559459993e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.391474295177943e-06</v>
+        <v>-3.391534561192344e-06</v>
       </c>
       <c r="T4" t="n">
         <v>1.219048280654e-06</v>
@@ -61180,13 +61180,13 @@
         <v>0.9999999999030202</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0014709992497903</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.011767993998323</v>
+        <v>0.0102969947485326</v>
       </c>
     </row>
     <row r="5">
@@ -61248,10 +61248,10 @@
         <v>0.0334823508181402</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.014278439250209</v>
+        <v>-0.0142786929763619</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0229580933708397</v>
+        <v>-0.0229585013334052</v>
       </c>
       <c r="T5" t="n">
         <v>0.0084532375356716</v>
@@ -61275,22 +61275,22 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.9900416352231036</v>
+        <v>0.990041423237908</v>
       </c>
       <c r="AB5" t="n">
         <v>0.7865255625611776</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.9971079588457348</v>
+        <v>0.997107831216269</v>
       </c>
       <c r="AD5" t="n">
-        <v>8.229505302952298</v>
+        <v>8.387698472972513</v>
       </c>
       <c r="AE5" t="n">
-        <v>4.511554699107104</v>
+        <v>4.538099441012062</v>
       </c>
       <c r="AF5" t="n">
-        <v>33.33431399949986</v>
+        <v>35.47461790794487</v>
       </c>
     </row>
     <row r="6">
@@ -61355,7 +61355,7 @@
         <v>-0.008465802234419799</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0203840281417675</v>
+        <v>-0.0203843903635025</v>
       </c>
       <c r="T6" t="n">
         <v>0.0036028508909026</v>
@@ -61379,22 +61379,22 @@
         <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.965047288221858</v>
+        <v>0.965046380306079</v>
       </c>
       <c r="AB6" t="n">
         <v>0.8326756929277627</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.9961020371450744</v>
+        <v>0.9961018651230008</v>
       </c>
       <c r="AD6" t="n">
-        <v>16.3052911843015</v>
+        <v>14.98580485723952</v>
       </c>
       <c r="AE6" t="n">
-        <v>6.03698092113973</v>
+        <v>4.404171753872405</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.26986952236654</v>
+        <v>34.32723849310837</v>
       </c>
     </row>
     <row r="7">
@@ -61483,22 +61483,22 @@
         <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.9777422983673296</v>
+        <v>0.9777416995812288</v>
       </c>
       <c r="AB7" t="n">
         <v>0.8883742282370569</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.997179982717303</v>
+        <v>0.9971798582663428</v>
       </c>
       <c r="AD7" t="n">
-        <v>12.11956281902296</v>
+        <v>12.42121868553004</v>
       </c>
       <c r="AE7" t="n">
-        <v>3.954045983436549</v>
+        <v>3.949632985687177</v>
       </c>
       <c r="AF7" t="n">
-        <v>26.07199070328474</v>
+        <v>27.91073976552272</v>
       </c>
     </row>
     <row r="8">
@@ -61560,7 +61560,7 @@
         <v>0.002586107326526</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0022178754135085</v>
+        <v>0.0022178930887115</v>
       </c>
       <c r="S8" t="n">
         <v>-0.0011223259841978</v>
@@ -61596,13 +61596,13 @@
         <v>0.997917012300089</v>
       </c>
       <c r="AD8" t="n">
-        <v>6.610670628557979</v>
+        <v>4.712385673897193</v>
       </c>
       <c r="AE8" t="n">
-        <v>4.729262588076081</v>
+        <v>2.693399626366191</v>
       </c>
       <c r="AF8" t="n">
-        <v>12.06366484753093</v>
+        <v>10.24550977479002</v>
       </c>
     </row>
     <row r="9">
@@ -61700,13 +61700,13 @@
         <v>0.996106857592908</v>
       </c>
       <c r="AD9" t="n">
-        <v>9.754196025360027</v>
+        <v>6.843824009649754</v>
       </c>
       <c r="AE9" t="n">
-        <v>7.140230358482517</v>
+        <v>4.074667921919359</v>
       </c>
       <c r="AF9" t="n">
-        <v>25.88076080081199</v>
+        <v>24.97609626219091</v>
       </c>
     </row>
     <row r="10">
@@ -61768,13 +61768,13 @@
         <v>0.041090481211723</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.0002267862465484</v>
+        <v>-0.0002296042173604</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0040754803118541</v>
+        <v>-0.0040781233768993</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0220689137860818</v>
+        <v>0.0220665383606984</v>
       </c>
       <c r="U10" t="n">
         <v>1</v>
@@ -61795,22 +61795,22 @@
         <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.9931421415819488</v>
+        <v>0.993227477861067</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9296884622085644</v>
+        <v>0.9297568037148356</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.996934518996488</v>
+        <v>0.9970204566981278</v>
       </c>
       <c r="AD10" t="n">
-        <v>11.32595872376105</v>
+        <v>6.568843777581643</v>
       </c>
       <c r="AE10" t="n">
-        <v>8.021358909106958</v>
+        <v>3.024418946749044</v>
       </c>
       <c r="AF10" t="n">
-        <v>25.56008296435769</v>
+        <v>23.10091203295087</v>
       </c>
     </row>
     <row r="11">
@@ -61872,13 +61872,13 @@
         <v>0.007648897371003</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.0034650513735485</v>
+        <v>-0.0034679484886296</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0069029830976754</v>
+        <v>-0.0069057168033808</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0005087241805041</v>
+        <v>0.0005060283627471</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -61899,22 +61899,22 @@
         <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.9982816177358262</v>
+        <v>0.9983694012138165</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9967285551792467</v>
+        <v>0.996816385403497</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.9991613963406464</v>
+        <v>0.999249518052284</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.643385651873317</v>
+        <v>1.585025007355104</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.406554772657066</v>
+        <v>0.9944101206237128</v>
       </c>
       <c r="AF11" t="n">
-        <v>4.204115855900914</v>
+        <v>3.505442777287437</v>
       </c>
     </row>
     <row r="12">
@@ -61976,10 +61976,10 @@
         <v>0.029081335912853</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0006891691340375</v>
+        <v>0.0006891757631186999</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0017018703419033</v>
+        <v>-0.0017019005839352</v>
       </c>
       <c r="T12" t="n">
         <v>0.0182893995721156</v>
@@ -62003,7 +62003,7 @@
         <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.9998086106947384</v>
+        <v>0.9998086064012101</v>
       </c>
       <c r="AB12" t="n">
         <v>0.9430628905817736</v>
@@ -62012,13 +62012,13 @@
         <v>0.9999990651899384</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.137817919712861</v>
+        <v>1.145172915961813</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.0470719759932922</v>
+        <v>0.0294199849958076</v>
       </c>
       <c r="AF12" t="n">
-        <v>13.44052014533472</v>
+        <v>14.28781571321399</v>
       </c>
     </row>
   </sheetData>
@@ -62703,7 +62703,7 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>3.460466819811521</v>
+        <v>3.460466819811497</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -64503,7 +64503,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>3.460487202006722</v>
+        <v>3.460487202006723</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -66303,7 +66303,7 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>3.460719287832846</v>
+        <v>3.460719287832843</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
